--- a/data/trans_bre/IP17-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 9,42</t>
+          <t>-12,11; 7,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 10,33</t>
+          <t>-8,81; 11,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 27,31</t>
+          <t>1,93; 26,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 7,39</t>
+          <t>-14,48; 7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 54,06</t>
+          <t>-42,29; 38,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 69,13</t>
+          <t>-36,01; 81,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 219,66</t>
+          <t>5,94; 237,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 78,99</t>
+          <t>-67,72; 74,52</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 1,25</t>
+          <t>-7,34; 1,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 1,96</t>
+          <t>-6,92; 1,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,73</t>
+          <t>-4,51; 3,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 0,91</t>
+          <t>-7,58; 1,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 7,06</t>
+          <t>-31,05; 6,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 8,71</t>
+          <t>-25,51; 7,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 21,02</t>
+          <t>-20,36; 21,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 5,5</t>
+          <t>-37,73; 7,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,31</t>
+          <t>-9,55; 5,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 15,82</t>
+          <t>0,85; 16,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,43</t>
+          <t>-8,66; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 8,5</t>
+          <t>-5,28; 9,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 23,93</t>
+          <t>-35,99; 33,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 109,16</t>
+          <t>2,34; 106,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 32,35</t>
+          <t>-35,59; 33,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 64,99</t>
+          <t>-25,61; 72,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,56</t>
+          <t>-6,66; 0,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,02</t>
+          <t>-3,85; 3,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,43</t>
+          <t>-2,71; 4,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 1,07</t>
+          <t>-5,95; 1,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 2,78</t>
+          <t>-27,3; 1,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 18,76</t>
+          <t>-15,59; 18,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 25,54</t>
+          <t>-12,32; 22,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 6,59</t>
+          <t>-31,47; 10,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 7,2</t>
+          <t>-11,26; 8,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 11,59</t>
+          <t>-8,85; 10,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 26,97</t>
+          <t>3,03; 27,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 7,4</t>
+          <t>-14,64; 6,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 38,69</t>
+          <t>-38,93; 48,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 81,15</t>
+          <t>-34,49; 75,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 237,69</t>
+          <t>6,35; 227,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,72; 74,52</t>
+          <t>-68,22; 71,51</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 1,25</t>
+          <t>-7,44; 1,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,63</t>
+          <t>-7,24; 1,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 3,9</t>
+          <t>-4,34; 3,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 1,24</t>
+          <t>-7,66; 1,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 6,0</t>
+          <t>-30,45; 6,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 7,09</t>
+          <t>-26,43; 7,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 21,72</t>
+          <t>-20,04; 19,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 7,79</t>
+          <t>-38,97; 9,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 5,69</t>
+          <t>-9,99; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 16,18</t>
+          <t>1,09; 15,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 5,66</t>
+          <t>-8,09; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 9,01</t>
+          <t>-5,34; 9,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 33,06</t>
+          <t>-38,33; 20,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 106,15</t>
+          <t>4,78; 110,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 33,8</t>
+          <t>-34,96; 35,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 72,37</t>
+          <t>-25,11; 71,22</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,4</t>
+          <t>-6,14; 0,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,76</t>
+          <t>-3,33; 4,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,1</t>
+          <t>-2,62; 4,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,62</t>
+          <t>-5,89; 0,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 1,74</t>
+          <t>-25,85; 3,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 18,0</t>
+          <t>-13,31; 21,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 22,8</t>
+          <t>-12,8; 22,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 10,39</t>
+          <t>-30,79; 6,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,32%</t>
+          <t>-20,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 8,91</t>
+          <t>-11,32; 9,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 10,48</t>
+          <t>-9,42; 10,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 27,78</t>
+          <t>2,51; 27,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 6,7</t>
+          <t>-13,52; 7,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 48,45</t>
+          <t>-37,97; 54,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 75,18</t>
+          <t>-36,48; 69,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 227,06</t>
+          <t>6,66; 219,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 71,51</t>
+          <t>-62,54; 92,41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,25</t>
+          <t>-2,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-18,42%</t>
+          <t>-16,85%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 1,29</t>
+          <t>-7,48; 1,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 1,82</t>
+          <t>-7,08; 1,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 3,52</t>
+          <t>-4,4; 3,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 1,44</t>
+          <t>-7,31; 1,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 6,59</t>
+          <t>-30,73; 7,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 7,88</t>
+          <t>-26,07; 8,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 19,74</t>
+          <t>-20,46; 21,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 9,25</t>
+          <t>-36,21; 9,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 3,88</t>
+          <t>-9,57; 4,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 15,81</t>
+          <t>0,66; 15,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 5,66</t>
+          <t>-8,71; 5,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 9,08</t>
+          <t>-7,06; 7,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 20,26</t>
+          <t>-37,56; 23,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 110,71</t>
+          <t>1,68; 109,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 35,08</t>
+          <t>-37,59; 32,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 71,22</t>
+          <t>-33,6; 54,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-2,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,51%</t>
+          <t>-12,48%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 0,79</t>
+          <t>-6,2; 0,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 4,36</t>
+          <t>-3,36; 4,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,06</t>
+          <t>-2,61; 4,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,99</t>
+          <t>-6,21; 1,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 3,3</t>
+          <t>-25,64; 2,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 21,08</t>
+          <t>-13,9; 18,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 22,07</t>
+          <t>-12,18; 25,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 6,03</t>
+          <t>-31,87; 7,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,73</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-20,53%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.758776977904353</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8487707163570724</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>14.72794148552801</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.29031813254379</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07406865640664161</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.04216219276937653</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.8341953772357418</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.205327734472964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-11,32; 9,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,42; 10,33</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,51; 27,31</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,52; 7,66</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-37,97; 54,06</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-36,48; 69,13</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,66; 219,66</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-62,54; 92,41</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-11.32185997257957</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.417172036578114</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2.508193561424344</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.52428017429062</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3797363886140094</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3648232241053249</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.06657327372494756</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.625405933460513</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.422557332393726</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.33234767094866</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>27.31210479959716</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.660179970777619</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.540568144904648</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.6912828785054237</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.196582502862551</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.9240521194760831</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,97</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-14,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-10,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,02%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-16,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,48; 1,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,08; 1,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,4; 3,73</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 1,41</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-30,73; 7,06</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-26,07; 8,71</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-20,46; 21,02</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-36,21; 9,75</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.140397706256912</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.6607691996102</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2021987031658123</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.969226244374765</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.141356749487921</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1072540926586498</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01016776021017319</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1685303668824456</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,62</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8,27</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-7,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.478014446068737</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.076049054081109</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.398717327878387</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.308724080420334</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3072747216260711</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2607212385550312</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.2045720928825078</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3621204507200435</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,57; 4,31</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,66; 15,82</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,71; 5,43</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,06; 7,45</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-37,56; 23,93</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 109,16</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-37,59; 32,35</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-33,6; 54,52</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.247243389263963</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.955142507569078</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.729893152608711</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.406147930885289</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.07058762888826059</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.08707728286978027</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.2102196522676077</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.09751519298713959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-12,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-12,48%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.619098819435636</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>8.274275656784447</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.564012315555385</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.4427676223703492</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1175106130398348</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.45766897452172</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.07797220429785738</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.02587104032034363</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,2; 0,56</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,36; 4,02</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 4,43</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,21; 1,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-25,64; 2,78</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-13,9; 18,76</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-12,18; 25,54</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-31,87; 7,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.570845427617122</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.6619613445274308</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.714911477419909</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.058122335583551</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3756484861454711</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.01677472282316844</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3758548457312775</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3360158260059284</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.313554648727369</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>15.82102217025086</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.425471140980038</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.447911436291625</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2393244804355324</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.091604067888009</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3235285750219259</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5451564310552954</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.800081129110066</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2527544664326892</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.742484680828992</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.167484207087691</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1249153187442583</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.01112135088577743</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.03764575658544685</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1247958582255401</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.200659967678433</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.362724236712632</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.61348695625298</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.206936874210676</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2564023865507492</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.138983403130014</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1217768689652747</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3186971681934727</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5623350271881813</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.020274170894363</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.431683644868994</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.187321342895656</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.02776620587375216</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1876255560997891</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2553692873691689</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.07427531565110645</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
